--- a/spec-tech/ig/StructureDefinition-pdlgcSystem.xlsx
+++ b/spec-tech/ig/StructureDefinition-pdlgcSystem.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-23T14:32:10+00:00</t>
+    <t>2026-07-23T16:03:49+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -276,7 +276,7 @@
 </t>
   </si>
   <si>
-    <t>Identifiant du logiciel</t>
+    <t>SystIdNat</t>
   </si>
 </sst>
 </file>

--- a/spec-tech/ig/StructureDefinition-pdlgcSystem.xlsx
+++ b/spec-tech/ig/StructureDefinition-pdlgcSystem.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-23T16:03:49+00:00</t>
+    <t>2026-07-23T16:11:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -272,11 +272,11 @@
     <t>pdlgcSystem.lgcIdentifiant</t>
   </si>
   <si>
-    <t xml:space="preserve">Identifier
+    <t xml:space="preserve">https://interop.esante.gouv.fr/ig/fhir/pdlgc/StructureDefinition/systIdNat
 </t>
   </si>
   <si>
-    <t>SystIdNat</t>
+    <t>Identifiant du système</t>
   </si>
 </sst>
 </file>
@@ -591,7 +591,7 @@
     <col min="8" max="8" width="13.953125" customWidth="true" bestFit="true"/>
     <col min="9" max="9" width="11.3671875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="7.9765625" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="57.4296875" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>

--- a/spec-tech/ig/StructureDefinition-pdlgcSystem.xlsx
+++ b/spec-tech/ig/StructureDefinition-pdlgcSystem.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-23T16:11:23+00:00</t>
+    <t>2026-07-27T13:36:25+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/spec-tech/ig/StructureDefinition-pdlgcSystem.xlsx
+++ b/spec-tech/ig/StructureDefinition-pdlgcSystem.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="197" uniqueCount="87">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="166" uniqueCount="85">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-27T13:36:25+00:00</t>
+    <t>2026-07-30T09:32:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -250,33 +250,27 @@
     <t>Base</t>
   </si>
   <si>
-    <t>pdlgcSystem.lgcNom</t>
+    <t>pdlgcSystem.lgcSoftwareVendor</t>
   </si>
   <si>
     <t>1</t>
   </si>
   <si>
-    <t xml:space="preserve">string
+    <t xml:space="preserve">https://interop.esante.gouv.fr/ig/fhir/pdlgc/StructureDefinition/pdlgcSoftwareVendor
 </t>
   </si>
   <si>
-    <t>Nom du logiciel</t>
-  </si>
-  <si>
-    <t>pdlgcSystem.lgcVersion</t>
-  </si>
-  <si>
-    <t>Version du logiciel</t>
-  </si>
-  <si>
-    <t>pdlgcSystem.lgcIdentifiant</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://interop.esante.gouv.fr/ig/fhir/pdlgc/StructureDefinition/systIdNat
+    <t>Editeur du logiciel responsable de la production et de l'export de l'archive de portabilité</t>
+  </si>
+  <si>
+    <t>pdlgcSystem.lgcSystem</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://interop.esante.gouv.fr/ig/fhir/pdlgc/StructureDefinition/xdmActorSystem
 </t>
   </si>
   <si>
-    <t>Identifiant du système</t>
+    <t>Logiciel responsable de la production et de l'export de l'archive de portabilité</t>
   </si>
 </sst>
 </file>
@@ -578,11 +572,11 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AJ5"/>
+  <dimension ref="A1:AJ4"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="21.890625" customWidth="true" bestFit="true"/>
-    <col min="2" max="2" width="21.890625" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="26.484375" customWidth="true" bestFit="true"/>
+    <col min="2" max="2" width="26.484375" customWidth="true" bestFit="true"/>
     <col min="3" max="3" width="10.8515625" customWidth="true" bestFit="true" hidden="true"/>
     <col min="4" max="4" width="7.6796875" customWidth="true" bestFit="true" hidden="true"/>
     <col min="5" max="5" width="5.80859375" customWidth="true" bestFit="true"/>
@@ -591,7 +585,7 @@
     <col min="8" max="8" width="13.953125" customWidth="true" bestFit="true"/>
     <col min="9" max="9" width="11.3671875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="57.4296875" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="66.95703125" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>
@@ -612,7 +606,7 @@
     <col min="29" max="29" width="17.65625" customWidth="true" bestFit="true"/>
     <col min="30" max="30" width="14.7578125" customWidth="true" bestFit="true"/>
     <col min="31" max="31" width="12.359375" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="32" max="32" width="21.890625" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="32" max="32" width="26.484375" customWidth="true" bestFit="true" hidden="true"/>
     <col min="33" max="33" width="9.046875" customWidth="true" bestFit="true" hidden="true"/>
     <col min="34" max="34" width="9.46484375" customWidth="true" bestFit="true"/>
     <col min="35" max="35" width="100.703125" customWidth="true"/>
@@ -956,13 +950,13 @@
         <v>73</v>
       </c>
       <c r="K4" t="s" s="2">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="L4" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="M4" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="N4" s="2"/>
       <c r="O4" s="2"/>
@@ -1025,106 +1019,6 @@
         <v>73</v>
       </c>
       <c r="AJ4" t="s" s="2">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="B5" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="C5" s="2"/>
-      <c r="D5" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="E5" s="2"/>
-      <c r="F5" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="G5" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="H5" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="I5" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="J5" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="K5" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="L5" t="s" s="2">
-        <v>86</v>
-      </c>
-      <c r="M5" t="s" s="2">
-        <v>86</v>
-      </c>
-      <c r="N5" s="2"/>
-      <c r="O5" s="2"/>
-      <c r="P5" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="Q5" s="2"/>
-      <c r="R5" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="S5" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="T5" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="U5" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="V5" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="W5" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="X5" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="Y5" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="Z5" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AA5" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AB5" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AC5" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AD5" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AE5" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AF5" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AG5" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AH5" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AI5" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AJ5" t="s" s="2">
         <v>73</v>
       </c>
     </row>
